--- a/events/LiptovskyMikulas_2015_WC/LiptovskyMikulas_2015_WC_start.xlsx
+++ b/events/LiptovskyMikulas_2015_WC/LiptovskyMikulas_2015_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W715"/>
+  <dimension ref="A1:AC715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1605,7 @@
           <t>LUKASS Andars</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>44865</t>
         </is>
@@ -1686,7 +1716,7 @@
           <t>KHAVANTSEV Valeriy</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>61157</t>
         </is>
@@ -1744,7 +1774,7 @@
           <t>PUTNINS Emils</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>63159</t>
         </is>
@@ -1802,7 +1832,7 @@
           <t>BONDAR Oleksandr</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>61371</t>
         </is>
@@ -1860,7 +1890,7 @@
           <t>YILMAZ Emre</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>60067</t>
         </is>
@@ -1918,7 +1948,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -1976,7 +2006,7 @@
           <t>OZOLS Kriss</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>48993</t>
         </is>
@@ -2034,7 +2064,7 @@
           <t>BULLO Carlo</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>35226</t>
         </is>
@@ -2092,7 +2122,7 @@
           <t>PAVLENKO Dmytro</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>42272</t>
         </is>
@@ -2150,7 +2180,7 @@
           <t>DEMIRCI Ismail</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>39914</t>
         </is>
@@ -2208,7 +2238,7 @@
           <t>SERRA Thiago</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
@@ -2266,7 +2296,7 @@
           <t>BLAISE Thibault</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>41589</t>
         </is>
@@ -2324,7 +2354,7 @@
           <t>DENNIS Tad</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>42253</t>
         </is>
@@ -2382,7 +2412,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -2440,7 +2470,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -2498,7 +2528,7 @@
           <t>TIMAKOV Dmitriy</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>53527</t>
         </is>
@@ -2556,7 +2586,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -2614,7 +2644,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -2672,7 +2702,7 @@
           <t>SMIRNOV Pavel</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>39135</t>
         </is>
@@ -2783,7 +2813,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -2841,7 +2871,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -2899,7 +2929,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -2957,7 +2987,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -3068,7 +3098,7 @@
           <t>HETSMAN Anton</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>41691</t>
         </is>
@@ -3126,7 +3156,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -3184,7 +3214,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -3295,7 +3325,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -3353,7 +3383,7 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -3411,7 +3441,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -3469,7 +3499,7 @@
           <t>GARMENDIA Aitor</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>35745</t>
         </is>
@@ -3580,7 +3610,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -3638,7 +3668,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -3696,7 +3726,7 @@
           <t>TRATSIAK Viktar</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>35270</t>
         </is>
@@ -3754,7 +3784,7 @@
           <t>PFEIFFER Frederick</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>39878</t>
         </is>
@@ -3812,7 +3842,7 @@
           <t>GONDEK Kacper</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>35472</t>
         </is>
@@ -3870,7 +3900,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -3928,7 +3958,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -3986,7 +4016,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -4044,7 +4074,7 @@
           <t>ERGUIN Jon</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>35740</t>
         </is>
@@ -4102,7 +4132,7 @@
           <t>LIPATOV Aleksandr</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>35451</t>
         </is>
@@ -4160,7 +4190,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -4218,7 +4248,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -4276,7 +4306,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -4334,7 +4364,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -4392,7 +4422,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -4450,7 +4480,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -4508,7 +4538,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -4566,7 +4596,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -4624,7 +4654,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -4682,7 +4712,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -4740,7 +4770,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -4798,7 +4828,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -4856,7 +4886,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -4914,7 +4944,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -4972,7 +5002,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -5030,7 +5060,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -5088,7 +5118,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -5146,7 +5176,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -5204,7 +5234,7 @@
           <t>DUANGLAHWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -5262,7 +5292,7 @@
           <t>MURZINA Juta</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>39930</t>
         </is>
@@ -5320,7 +5350,7 @@
           <t>BREGAZZI Ella</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>41598</t>
         </is>
@@ -5378,7 +5408,7 @@
           <t>KRAUJA Santa</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>42927</t>
         </is>
@@ -5489,7 +5519,7 @@
           <t>JUETTNER Rebekka</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>51836</t>
         </is>
@@ -5600,7 +5630,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -5711,7 +5741,7 @@
           <t>JANCZY Justyna</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>43975</t>
         </is>
@@ -5769,7 +5799,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -5827,7 +5857,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -5885,7 +5915,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -5943,7 +5973,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -6001,7 +6031,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -6059,7 +6089,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -6117,7 +6147,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -6175,7 +6205,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -6233,7 +6263,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -6291,7 +6321,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -6349,7 +6379,7 @@
           <t>RANKIN Georgia</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>38435</t>
         </is>
@@ -6407,7 +6437,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -6465,7 +6495,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -6523,7 +6553,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -6581,7 +6611,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -6639,7 +6669,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -6697,7 +6727,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>35309</t>
         </is>
@@ -6755,7 +6785,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -6813,7 +6843,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -6977,7 +7007,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -7088,7 +7118,7 @@
           <t>PESTOV Ruslan</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>36138</t>
         </is>
@@ -7146,7 +7176,7 @@
           <t>MYAGKIY Yuriy</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>61159</t>
         </is>
@@ -7204,7 +7234,7 @@
           <t>ABDUMUROTOV Tulkin</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>61160</t>
         </is>
@@ -7262,7 +7292,7 @@
           <t>TARKKA Teijo</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>35804</t>
         </is>
@@ -7320,7 +7350,7 @@
           <t>RASIMAVICIUS Vilius</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>36965</t>
         </is>
@@ -7378,7 +7408,7 @@
           <t>PAKERS Kaspars</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>42940</t>
         </is>
@@ -7436,7 +7466,7 @@
           <t>NIKOLOVSKI Atanas</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>35582</t>
         </is>
@@ -7494,7 +7524,7 @@
           <t>ACAR Anil</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>39900</t>
         </is>
@@ -7552,7 +7582,7 @@
           <t>CELMINS Ritvars</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>35182</t>
         </is>
@@ -7610,7 +7640,7 @@
           <t>SHABANOV Maxim</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
@@ -7668,7 +7698,7 @@
           <t>RYAN Cade</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>37919</t>
         </is>
@@ -7726,7 +7756,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -7784,7 +7814,7 @@
           <t>ATMANAVICIUS Mantas</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>35619</t>
         </is>
@@ -7842,7 +7872,7 @@
           <t>SMITH Tyler</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
@@ -7900,7 +7930,7 @@
           <t>NABASKUES Unai</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>38775</t>
         </is>
@@ -7958,7 +7988,7 @@
           <t>BEDA Marcello</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>39899</t>
         </is>
@@ -8016,7 +8046,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -8074,7 +8104,7 @@
           <t>MAXEINER Tim</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
@@ -8132,7 +8162,7 @@
           <t>URANO Shuhei</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>44317</t>
         </is>
@@ -8190,7 +8220,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -8248,7 +8278,7 @@
           <t>DAMIENS Bastien</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>35584</t>
         </is>
@@ -8306,7 +8336,7 @@
           <t>CVIKL Ondrej</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>35946</t>
         </is>
@@ -8364,7 +8394,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -8422,7 +8452,7 @@
           <t>DAVIDSON Elliott</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>43077</t>
         </is>
@@ -8480,7 +8510,7 @@
           <t>PAN Hung-Ming</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>37001</t>
         </is>
@@ -8538,7 +8568,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -8596,7 +8626,7 @@
           <t>CORDERO Matias</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>36918</t>
         </is>
@@ -8654,7 +8684,7 @@
           <t>MARTINS TAQUES Ricardo</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>38022</t>
         </is>
@@ -8765,7 +8795,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -8823,7 +8853,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -8881,7 +8911,7 @@
           <t>KANAYA Tohru</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>36484</t>
         </is>
@@ -8939,7 +8969,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -8997,7 +9027,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -9055,7 +9085,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -9113,7 +9143,7 @@
           <t>KARAMARKO Filip</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>35596</t>
         </is>
@@ -9171,7 +9201,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -9229,7 +9259,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -9287,7 +9317,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -9345,7 +9375,7 @@
           <t>SCIANIMANICO Tom</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>35675</t>
         </is>
@@ -9403,7 +9433,7 @@
           <t>MRKOCI Marko</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>35592</t>
         </is>
@@ -9461,7 +9491,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -9519,7 +9549,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -9577,7 +9607,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -9635,7 +9665,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -9746,7 +9776,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -9804,7 +9834,7 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -9862,7 +9892,7 @@
           <t>RAIBA Omar</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>35501</t>
         </is>
@@ -9920,7 +9950,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -9978,7 +10008,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -10036,7 +10066,7 @@
           <t>LANGER Andreas</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>35295</t>
         </is>
@@ -10094,7 +10124,7 @@
           <t>BURGI Quentin</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>41590</t>
         </is>
@@ -10152,7 +10182,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -10263,7 +10293,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -10374,7 +10404,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -10432,7 +10462,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -10490,7 +10520,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -10601,7 +10631,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -10712,7 +10742,7 @@
           <t>MEGLIC Jure</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>35590</t>
         </is>
@@ -10770,7 +10800,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -10828,7 +10858,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -10886,7 +10916,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -10944,7 +10974,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -11002,7 +11032,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -11060,7 +11090,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -11118,7 +11148,7 @@
           <t>KURT Michael</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>35346</t>
         </is>
@@ -11176,7 +11206,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -11234,7 +11264,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -11292,7 +11322,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -11350,7 +11380,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -11408,7 +11438,7 @@
           <t>BOECKELMANN Paul</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>35118</t>
         </is>
@@ -11466,7 +11496,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -11524,7 +11554,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -11582,7 +11612,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -11640,7 +11670,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -11698,7 +11728,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -11756,7 +11786,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -11814,7 +11844,7 @@
           <t>LUKASS Andars</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>44865</t>
         </is>
@@ -11925,7 +11955,7 @@
           <t>KHAVANTSEV Valeriy</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>61157</t>
         </is>
@@ -11983,7 +12013,7 @@
           <t>PUTNINS Emils</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>63159</t>
         </is>
@@ -12041,7 +12071,7 @@
           <t>BONDAR Oleksandr</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>61371</t>
         </is>
@@ -12099,7 +12129,7 @@
           <t>YILMAZ Emre</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>60067</t>
         </is>
@@ -12157,7 +12187,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -12215,7 +12245,7 @@
           <t>OZOLS Kriss</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>48993</t>
         </is>
@@ -12273,7 +12303,7 @@
           <t>BULLO Carlo</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>35226</t>
         </is>
@@ -12331,7 +12361,7 @@
           <t>PAVLENKO Dmytro</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>42272</t>
         </is>
@@ -12389,7 +12419,7 @@
           <t>DEMIRCI Ismail</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>39914</t>
         </is>
@@ -12447,7 +12477,7 @@
           <t>SERRA Thiago</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
@@ -12505,7 +12535,7 @@
           <t>BLAISE Thibault</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>41589</t>
         </is>
@@ -12563,7 +12593,7 @@
           <t>DENNIS Tad</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>42253</t>
         </is>
@@ -12621,7 +12651,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -12679,7 +12709,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -12737,7 +12767,7 @@
           <t>TIMAKOV Dmitriy</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>53527</t>
         </is>
@@ -12795,7 +12825,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -12853,7 +12883,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -12911,7 +12941,7 @@
           <t>SMIRNOV Pavel</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>39135</t>
         </is>
@@ -13022,7 +13052,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -13080,7 +13110,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -13191,7 +13221,7 @@
           <t>HETSMAN Anton</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>41691</t>
         </is>
@@ -13249,7 +13279,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -13307,7 +13337,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -13418,7 +13448,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -13476,7 +13506,7 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -13534,7 +13564,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -13592,7 +13622,7 @@
           <t>GARMENDIA Aitor</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>35745</t>
         </is>
@@ -13703,7 +13733,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -13761,7 +13791,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -13819,7 +13849,7 @@
           <t>TRATSIAK Viktar</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>35270</t>
         </is>
@@ -13877,7 +13907,7 @@
           <t>PFEIFFER Frederick</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>39878</t>
         </is>
@@ -13935,7 +13965,7 @@
           <t>GONDEK Kacper</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>35472</t>
         </is>
@@ -13993,7 +14023,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -14051,7 +14081,7 @@
           <t>ERGUIN Jon</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>35740</t>
         </is>
@@ -14109,7 +14139,7 @@
           <t>LIPATOV Aleksandr</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>35451</t>
         </is>
@@ -14167,7 +14197,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -14225,7 +14255,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -14283,7 +14313,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -14341,7 +14371,7 @@
           <t>DUANGLAHWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -14399,7 +14429,7 @@
           <t>MURZINA Juta</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>39930</t>
         </is>
@@ -14457,7 +14487,7 @@
           <t>BREGAZZI Ella</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>41598</t>
         </is>
@@ -14515,7 +14545,7 @@
           <t>KRAUJA Santa</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>42927</t>
         </is>
@@ -14626,7 +14656,7 @@
           <t>JUETTNER Rebekka</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>51836</t>
         </is>
@@ -14790,7 +14820,7 @@
           <t>JANCZY Justyna</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>43975</t>
         </is>
@@ -14848,7 +14878,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -14906,7 +14936,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -14964,7 +14994,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -15022,7 +15052,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -15080,7 +15110,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -15138,7 +15168,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -15196,7 +15226,7 @@
           <t>RANKIN Georgia</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>38435</t>
         </is>
@@ -15254,7 +15284,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -15312,7 +15342,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -15370,7 +15400,7 @@
           <t>PESTOV Ruslan</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>36138</t>
         </is>
@@ -15428,7 +15458,7 @@
           <t>MYAGKIY Yuriy</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>61159</t>
         </is>
@@ -15486,7 +15516,7 @@
           <t>ABDUMUROTOV Tulkin</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>61160</t>
         </is>
@@ -15544,7 +15574,7 @@
           <t>TARKKA Teijo</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>35804</t>
         </is>
@@ -15602,7 +15632,7 @@
           <t>RASIMAVICIUS Vilius</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>36965</t>
         </is>
@@ -15660,7 +15690,7 @@
           <t>PAKERS Kaspars</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>42940</t>
         </is>
@@ -15718,7 +15748,7 @@
           <t>NIKOLOVSKI Atanas</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>35582</t>
         </is>
@@ -15776,7 +15806,7 @@
           <t>ACAR Anil</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>39900</t>
         </is>
@@ -15834,7 +15864,7 @@
           <t>CELMINS Ritvars</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>35182</t>
         </is>
@@ -15892,7 +15922,7 @@
           <t>SHABANOV Maxim</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
@@ -15950,7 +15980,7 @@
           <t>RYAN Cade</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>37919</t>
         </is>
@@ -16008,7 +16038,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -16066,7 +16096,7 @@
           <t>ATMANAVICIUS Mantas</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>35619</t>
         </is>
@@ -16124,7 +16154,7 @@
           <t>SMITH Tyler</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
@@ -16182,7 +16212,7 @@
           <t>NABASKUES Unai</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>38775</t>
         </is>
@@ -16240,7 +16270,7 @@
           <t>BEDA Marcello</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>39899</t>
         </is>
@@ -16298,7 +16328,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -16356,7 +16386,7 @@
           <t>URANO Shuhei</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>44317</t>
         </is>
@@ -16414,7 +16444,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -16472,7 +16502,7 @@
           <t>DAMIENS Bastien</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>35584</t>
         </is>
@@ -16530,7 +16560,7 @@
           <t>CVIKL Ondrej</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>35946</t>
         </is>
@@ -16588,7 +16618,7 @@
           <t>DAVIDSON Elliott</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>43077</t>
         </is>
@@ -16646,7 +16676,7 @@
           <t>PAN Hung-Ming</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>37001</t>
         </is>
@@ -16704,7 +16734,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -16762,7 +16792,7 @@
           <t>CORDERO Matias</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>36918</t>
         </is>
@@ -16820,7 +16850,7 @@
           <t>MARTINS TAQUES Ricardo</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>38022</t>
         </is>
@@ -16931,7 +16961,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -16989,7 +17019,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -17047,7 +17077,7 @@
           <t>KANAYA Tohru</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>36484</t>
         </is>
@@ -17105,7 +17135,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -17163,7 +17193,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -17221,7 +17251,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -17279,7 +17309,7 @@
           <t>KARAMARKO Filip</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>35596</t>
         </is>
@@ -17337,7 +17367,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -17395,7 +17425,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -17453,7 +17483,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -17511,7 +17541,7 @@
           <t>SCIANIMANICO Tom</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>35675</t>
         </is>
@@ -17569,7 +17599,7 @@
           <t>MRKOCI Marko</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>35592</t>
         </is>
@@ -17627,7 +17657,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -17685,7 +17715,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -17796,7 +17826,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -17854,7 +17884,7 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -17912,7 +17942,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -17970,7 +18000,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -18028,7 +18058,7 @@
           <t>LANGER Andreas</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>35295</t>
         </is>
@@ -18245,7 +18275,7 @@
           <t>MEGLIC Jure</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>35590</t>
         </is>
@@ -18303,7 +18333,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -18414,7 +18444,7 @@
           <t>FAGERLUND Amanda</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>43406</t>
         </is>
@@ -18472,7 +18502,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -18530,7 +18560,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -18588,7 +18618,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -18646,7 +18676,7 @@
           <t>CWIK Sara</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>43978</t>
         </is>
@@ -18757,7 +18787,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -18815,7 +18845,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -18926,7 +18956,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -18984,7 +19014,7 @@
           <t>DANGEN Haylee</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>42108</t>
         </is>
@@ -19042,7 +19072,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -19153,7 +19183,7 @@
           <t>DENHOLLANDER Jazmyne</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>37165</t>
         </is>
@@ -19211,7 +19241,7 @@
           <t>FROEHLICH Thea</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>35533</t>
         </is>
@@ -19269,7 +19299,7 @@
           <t>NICHOLAS Ella</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>36591</t>
         </is>
@@ -19327,7 +19357,7 @@
           <t>CRAIG Hannah</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
@@ -19385,7 +19415,7 @@
           <t>ZARUBOVA Kristina</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>39247</t>
         </is>
@@ -19443,7 +19473,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -19501,7 +19531,7 @@
           <t>ISMAILOVA Sevinch</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>35269</t>
         </is>
@@ -19559,7 +19589,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -19617,7 +19647,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -19675,7 +19705,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -19733,7 +19763,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -19791,7 +19821,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -19849,7 +19879,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -19907,7 +19937,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -19965,7 +19995,7 @@
           <t>GUIET Pauline</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>35493</t>
         </is>
@@ -20023,7 +20053,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -20134,7 +20164,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -20192,7 +20222,7 @@
           <t>MANGIN Estelle</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>35670</t>
         </is>
@@ -20250,7 +20280,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -20308,7 +20338,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -20366,7 +20396,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -20424,7 +20454,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -20482,7 +20512,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -20540,7 +20570,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -20598,7 +20628,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -20656,7 +20686,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -20714,7 +20744,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -20772,7 +20802,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -20830,7 +20860,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -20888,7 +20918,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -20946,7 +20976,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -21004,7 +21034,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -21062,7 +21092,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -21120,7 +21150,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -21231,7 +21261,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -21289,7 +21319,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -21347,7 +21377,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -21405,7 +21435,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -21463,7 +21493,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -21574,7 +21604,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -21637,12 +21667,12 @@
           <t>DENNIS Tad</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
       </c>
-      <c r="V371" t="inlineStr">
+      <c r="Y371" t="inlineStr">
         <is>
           <t>42253</t>
         </is>
@@ -21705,12 +21735,12 @@
           <t>KUCHKOROV Sirojiddin</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>61161</t>
         </is>
       </c>
-      <c r="V372" t="inlineStr">
+      <c r="Y372" t="inlineStr">
         <is>
           <t>61155</t>
         </is>
@@ -21773,12 +21803,12 @@
           <t>BONDAR Oleksandr</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>42877</t>
         </is>
       </c>
-      <c r="V373" t="inlineStr">
+      <c r="Y373" t="inlineStr">
         <is>
           <t>61371</t>
         </is>
@@ -21841,12 +21871,12 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
       </c>
-      <c r="V374" t="inlineStr">
+      <c r="Y374" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -21909,7 +21939,7 @@
           <t>DE SOUZA Rafael Augusto</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
+      <c r="X375" t="inlineStr">
         <is>
           <t>60498</t>
         </is>
@@ -21972,12 +22002,12 @@
           <t>MOTTAIS Martin</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>35690</t>
         </is>
       </c>
-      <c r="V376" t="inlineStr">
+      <c r="Y376" t="inlineStr">
         <is>
           <t>35691</t>
         </is>
@@ -22040,12 +22070,12 @@
           <t>SUSLOV Alexei</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
       </c>
-      <c r="V377" t="inlineStr">
+      <c r="Y377" t="inlineStr">
         <is>
           <t>35770</t>
         </is>
@@ -22108,12 +22138,12 @@
           <t>SKAKALA Juraj</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
       </c>
-      <c r="V378" t="inlineStr">
+      <c r="Y378" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
@@ -22176,7 +22206,7 @@
           <t>SASAKI Tsubasa</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -22239,12 +22269,12 @@
           <t>SCIANIMANICO Nicolas</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
       </c>
-      <c r="V380" t="inlineStr">
+      <c r="Y380" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
@@ -22307,12 +22337,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V381" t="inlineStr">
+      <c r="Y381" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -22375,12 +22405,12 @@
           <t>KERVELLA Loic</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V382" t="inlineStr">
+      <c r="Y382" t="inlineStr">
         <is>
           <t>35672</t>
         </is>
@@ -22443,12 +22473,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V383" t="inlineStr">
+      <c r="Y383" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -22511,12 +22541,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V384" t="inlineStr">
+      <c r="Y384" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -22579,12 +22609,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V385" t="inlineStr">
+      <c r="Y385" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -22647,7 +22677,7 @@
           <t>PITT Greg</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -22710,12 +22740,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V387" t="inlineStr">
+      <c r="Y387" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -22836,12 +22866,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V389" t="inlineStr">
+      <c r="Y389" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -22904,12 +22934,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V390" t="inlineStr">
+      <c r="Y390" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -22972,12 +23002,12 @@
           <t>LARIONOV Dmitry</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>35449</t>
         </is>
       </c>
-      <c r="V391" t="inlineStr">
+      <c r="Y391" t="inlineStr">
         <is>
           <t>35450</t>
         </is>
@@ -23040,12 +23070,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V392" t="inlineStr">
+      <c r="Y392" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -23108,12 +23138,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V393" t="inlineStr">
+      <c r="Y393" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -23176,12 +23206,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V394" t="inlineStr">
+      <c r="Y394" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -23244,12 +23274,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V395" t="inlineStr">
+      <c r="Y395" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -23312,12 +23342,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V396" t="inlineStr">
+      <c r="Y396" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -23380,12 +23410,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V397" t="inlineStr">
+      <c r="Y397" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -23448,12 +23478,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V398" t="inlineStr">
+      <c r="Y398" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -23516,12 +23546,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V399" t="inlineStr">
+      <c r="Y399" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -23584,7 +23614,7 @@
           <t>HOUNSLOW Richard</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -23647,12 +23677,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V401" t="inlineStr">
+      <c r="Y401" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -23715,12 +23745,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V402" t="inlineStr">
+      <c r="Y402" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -23783,12 +23813,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V403" t="inlineStr">
+      <c r="Y403" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -23899,7 +23929,7 @@
           <t>FAGERLUND Amanda</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>43406</t>
         </is>
@@ -23957,7 +23987,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -24015,7 +24045,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -24073,7 +24103,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -24131,7 +24161,7 @@
           <t>CWIK Sara</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>43978</t>
         </is>
@@ -24189,7 +24219,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -24247,7 +24277,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -24358,7 +24388,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -24416,7 +24446,7 @@
           <t>DANGEN Haylee</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>42108</t>
         </is>
@@ -24474,7 +24504,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -24585,7 +24615,7 @@
           <t>DENHOLLANDER Jazmyne</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>37165</t>
         </is>
@@ -24643,7 +24673,7 @@
           <t>FROEHLICH Thea</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>35533</t>
         </is>
@@ -24701,7 +24731,7 @@
           <t>NICHOLAS Ella</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>36591</t>
         </is>
@@ -24759,7 +24789,7 @@
           <t>CRAIG Hannah</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
@@ -24817,7 +24847,7 @@
           <t>ZARUBOVA Kristina</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>39247</t>
         </is>
@@ -24875,7 +24905,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -24933,7 +24963,7 @@
           <t>ISMAILOVA Sevinch</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>35269</t>
         </is>
@@ -24991,7 +25021,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -25049,7 +25079,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -25107,7 +25137,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -25165,7 +25195,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -25223,7 +25253,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -25281,7 +25311,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -25339,7 +25369,7 @@
           <t>GUIET Pauline</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>35493</t>
         </is>
@@ -25397,7 +25427,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -25508,7 +25538,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -25566,7 +25596,7 @@
           <t>MANGIN Estelle</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>35670</t>
         </is>
@@ -25624,7 +25654,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -25682,7 +25712,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -25740,7 +25770,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -25798,7 +25828,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -25856,7 +25886,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -25914,7 +25944,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -25972,7 +26002,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -26035,12 +26065,12 @@
           <t>DENNIS Tad</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
       </c>
-      <c r="V442" t="inlineStr">
+      <c r="Y442" t="inlineStr">
         <is>
           <t>42253</t>
         </is>
@@ -26103,12 +26133,12 @@
           <t>KUCHKOROV Sirojiddin</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>61161</t>
         </is>
       </c>
-      <c r="V443" t="inlineStr">
+      <c r="Y443" t="inlineStr">
         <is>
           <t>61155</t>
         </is>
@@ -26171,12 +26201,12 @@
           <t>BONDAR Oleksandr</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>42877</t>
         </is>
       </c>
-      <c r="V444" t="inlineStr">
+      <c r="Y444" t="inlineStr">
         <is>
           <t>61371</t>
         </is>
@@ -26239,12 +26269,12 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
       </c>
-      <c r="V445" t="inlineStr">
+      <c r="Y445" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -26307,12 +26337,12 @@
           <t>DE SOUZA Rafael</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>60498</t>
         </is>
       </c>
-      <c r="V446" t="inlineStr">
+      <c r="Y446" t="inlineStr">
         <is>
           <t>38021</t>
         </is>
@@ -26375,12 +26405,12 @@
           <t>MOTTAIS Martin</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>35690</t>
         </is>
       </c>
-      <c r="V447" t="inlineStr">
+      <c r="Y447" t="inlineStr">
         <is>
           <t>35691</t>
         </is>
@@ -26443,12 +26473,12 @@
           <t>SUSLOV Alexei</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
       </c>
-      <c r="V448" t="inlineStr">
+      <c r="Y448" t="inlineStr">
         <is>
           <t>35770</t>
         </is>
@@ -26511,12 +26541,12 @@
           <t>SKAKALA Juraj</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
       </c>
-      <c r="V449" t="inlineStr">
+      <c r="Y449" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
@@ -26579,7 +26609,7 @@
           <t>SASAKI Tsubasa</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -26642,12 +26672,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V451" t="inlineStr">
+      <c r="Y451" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -26710,12 +26740,12 @@
           <t>KERVELLA Loic</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V452" t="inlineStr">
+      <c r="Y452" t="inlineStr">
         <is>
           <t>35672</t>
         </is>
@@ -26778,12 +26808,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V453" t="inlineStr">
+      <c r="Y453" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -26846,12 +26876,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V454" t="inlineStr">
+      <c r="Y454" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -26914,12 +26944,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V455" t="inlineStr">
+      <c r="Y455" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -26982,7 +27012,7 @@
           <t>PITT Greg</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -27045,12 +27075,12 @@
           <t>LARIONOV Dmitry</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>35449</t>
         </is>
       </c>
-      <c r="V457" t="inlineStr">
+      <c r="Y457" t="inlineStr">
         <is>
           <t>35450</t>
         </is>
@@ -27113,12 +27143,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V458" t="inlineStr">
+      <c r="Y458" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -27181,12 +27211,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V459" t="inlineStr">
+      <c r="Y459" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -27562,7 +27592,7 @@
           <t>PFEIFFER Frederick</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>39878</t>
         </is>
@@ -27620,7 +27650,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -27678,7 +27708,7 @@
           <t>DENNIS Tad</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>42253</t>
         </is>
@@ -27736,7 +27766,7 @@
           <t>GONDEK Kacper</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>35472</t>
         </is>
@@ -27794,7 +27824,7 @@
           <t>LIPATOV Aleksandr</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>35451</t>
         </is>
@@ -27852,7 +27882,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -27910,7 +27940,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -27968,7 +27998,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -28026,7 +28056,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -28084,7 +28114,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -28142,7 +28172,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -28200,7 +28230,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -28258,7 +28288,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -28316,7 +28346,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -28374,7 +28404,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -28432,7 +28462,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -28490,7 +28520,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -28548,7 +28578,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -28606,7 +28636,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -28664,7 +28694,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -28722,7 +28752,7 @@
           <t>MARC Jonathan</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>35388</t>
         </is>
@@ -28780,7 +28810,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -28838,7 +28868,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -28896,7 +28926,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -28954,7 +28984,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -29012,7 +29042,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -29070,7 +29100,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -29128,7 +29158,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -29186,7 +29216,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -29244,7 +29274,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -29302,7 +29332,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -29360,7 +29390,7 @@
           <t>BREGAZZI Ella</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>41598</t>
         </is>
@@ -29418,7 +29448,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -29529,7 +29559,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -29587,7 +29617,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -29645,7 +29675,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -29703,7 +29733,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -29761,7 +29791,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -29819,7 +29849,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -29877,7 +29907,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -29935,7 +29965,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -29993,7 +30023,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -30051,7 +30081,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -30109,7 +30139,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>35309</t>
         </is>
@@ -30220,7 +30250,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -30278,7 +30308,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -30495,7 +30525,7 @@
           <t>CELMINS Ritvars</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>35182</t>
         </is>
@@ -30553,7 +30583,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -30611,7 +30641,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -30722,7 +30752,7 @@
           <t>DAMIENS Bastien</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>35584</t>
         </is>
@@ -30780,7 +30810,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -30838,7 +30868,7 @@
           <t>MEGLIC Jure</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>35590</t>
         </is>
@@ -31002,7 +31032,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -31060,7 +31090,7 @@
           <t>KURT Michael</t>
         </is>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="X527" t="inlineStr">
         <is>
           <t>35346</t>
         </is>
@@ -31118,7 +31148,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -31176,7 +31206,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U529" t="inlineStr">
+      <c r="X529" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -31234,7 +31264,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="X530" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -31292,7 +31322,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U531" t="inlineStr">
+      <c r="X531" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -31350,7 +31380,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -31408,7 +31438,7 @@
           <t>RAIBA Omar</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>35501</t>
         </is>
@@ -31466,7 +31496,7 @@
           <t>BOECKELMANN Paul</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>35118</t>
         </is>
@@ -31524,7 +31554,7 @@
           <t>MAXEINER Tim</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
@@ -31582,7 +31612,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U536" t="inlineStr">
+      <c r="X536" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -31640,7 +31670,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -31698,7 +31728,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -31756,7 +31786,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr">
+      <c r="X539" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -31814,7 +31844,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -31872,7 +31902,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -31930,7 +31960,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -31988,7 +32018,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -32046,7 +32076,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U544" t="inlineStr">
+      <c r="X544" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -32104,7 +32134,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -32162,7 +32192,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -32220,7 +32250,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -32278,7 +32308,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -32336,7 +32366,7 @@
           <t>BURGI Quentin</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>41590</t>
         </is>
@@ -32394,7 +32424,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -32452,7 +32482,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -32510,7 +32540,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -32568,7 +32598,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -32626,7 +32656,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U554" t="inlineStr">
+      <c r="X554" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -32684,7 +32714,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -32752,7 +32782,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -32820,7 +32850,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -32888,7 +32918,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -32956,7 +32986,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U559" t="inlineStr">
+      <c r="X559" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -33024,7 +33054,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -33092,7 +33122,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -33160,7 +33190,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U562" t="inlineStr">
+      <c r="X562" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -33228,7 +33258,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U563" t="inlineStr">
+      <c r="X563" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -33296,7 +33326,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U564" t="inlineStr">
+      <c r="X564" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -33364,7 +33394,7 @@
           <t>MARC Jonathan</t>
         </is>
       </c>
-      <c r="U565" t="inlineStr">
+      <c r="X565" t="inlineStr">
         <is>
           <t>35388</t>
         </is>
@@ -33432,7 +33462,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U566" t="inlineStr">
+      <c r="X566" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -33500,7 +33530,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U567" t="inlineStr">
+      <c r="X567" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -33631,7 +33661,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U569" t="inlineStr">
+      <c r="X569" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -33699,7 +33729,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U570" t="inlineStr">
+      <c r="X570" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -33767,7 +33797,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U571" t="inlineStr">
+      <c r="X571" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -33835,7 +33865,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U572" t="inlineStr">
+      <c r="X572" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -33966,7 +33996,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U574" t="inlineStr">
+      <c r="X574" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -34034,7 +34064,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U575" t="inlineStr">
+      <c r="X575" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -34102,7 +34132,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U576" t="inlineStr">
+      <c r="X576" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -34170,7 +34200,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U577" t="inlineStr">
+      <c r="X577" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -34238,7 +34268,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -34306,7 +34336,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -34374,7 +34404,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U580" t="inlineStr">
+      <c r="X580" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -34442,7 +34472,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U581" t="inlineStr">
+      <c r="X581" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -34510,7 +34540,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U582" t="inlineStr">
+      <c r="X582" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -34578,7 +34608,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U583" t="inlineStr">
+      <c r="X583" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -34646,7 +34676,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U584" t="inlineStr">
+      <c r="X584" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -34714,7 +34744,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U585" t="inlineStr">
+      <c r="X585" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -34792,17 +34822,17 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U586" t="inlineStr">
+      <c r="X586" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
       </c>
-      <c r="V586" t="inlineStr">
+      <c r="Y586" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
       </c>
-      <c r="W586" t="inlineStr">
+      <c r="Z586" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -34880,17 +34910,17 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U587" t="inlineStr">
+      <c r="X587" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
       </c>
-      <c r="V587" t="inlineStr">
+      <c r="Y587" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
       </c>
-      <c r="W587" t="inlineStr">
+      <c r="Z587" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -34968,12 +34998,12 @@
           <t>SERRA Thiago</t>
         </is>
       </c>
-      <c r="U588" t="inlineStr">
+      <c r="X588" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
       </c>
-      <c r="W588" t="inlineStr">
+      <c r="Z588" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
@@ -35051,17 +35081,17 @@
           <t>BULLO Carlo</t>
         </is>
       </c>
-      <c r="U589" t="inlineStr">
+      <c r="X589" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
       </c>
-      <c r="V589" t="inlineStr">
+      <c r="Y589" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
       </c>
-      <c r="W589" t="inlineStr">
+      <c r="Z589" t="inlineStr">
         <is>
           <t>35226</t>
         </is>
@@ -35139,17 +35169,17 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U590" t="inlineStr">
+      <c r="X590" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
       </c>
-      <c r="V590" t="inlineStr">
+      <c r="Y590" t="inlineStr">
         <is>
           <t>35472</t>
         </is>
       </c>
-      <c r="W590" t="inlineStr">
+      <c r="Z590" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -35227,17 +35257,17 @@
           <t>SMIRNOV Pavel</t>
         </is>
       </c>
-      <c r="U591" t="inlineStr">
+      <c r="X591" t="inlineStr">
         <is>
           <t>35451</t>
         </is>
       </c>
-      <c r="V591" t="inlineStr">
+      <c r="Y591" t="inlineStr">
         <is>
           <t>53527</t>
         </is>
       </c>
-      <c r="W591" t="inlineStr">
+      <c r="Z591" t="inlineStr">
         <is>
           <t>39135</t>
         </is>
@@ -35315,12 +35345,12 @@
           <t>HINTON Tyler</t>
         </is>
       </c>
-      <c r="U592" t="inlineStr">
+      <c r="X592" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
       </c>
-      <c r="V592" t="inlineStr">
+      <c r="Y592" t="inlineStr">
         <is>
           <t>42253</t>
         </is>
@@ -35388,17 +35418,17 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U593" t="inlineStr">
+      <c r="X593" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
       </c>
-      <c r="V593" t="inlineStr">
+      <c r="Y593" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
       </c>
-      <c r="W593" t="inlineStr">
+      <c r="Z593" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -35476,17 +35506,17 @@
           <t>GARMENDIA Aitor</t>
         </is>
       </c>
-      <c r="U594" t="inlineStr">
+      <c r="X594" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
       </c>
-      <c r="V594" t="inlineStr">
+      <c r="Y594" t="inlineStr">
         <is>
           <t>35740</t>
         </is>
       </c>
-      <c r="W594" t="inlineStr">
+      <c r="Z594" t="inlineStr">
         <is>
           <t>35745</t>
         </is>
@@ -35554,17 +35584,17 @@
           <t>PFEIFFER Frederick</t>
         </is>
       </c>
-      <c r="U595" t="inlineStr">
+      <c r="X595" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
       </c>
-      <c r="V595" t="inlineStr">
+      <c r="Y595" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
       </c>
-      <c r="W595" t="inlineStr">
+      <c r="Z595" t="inlineStr">
         <is>
           <t>39878</t>
         </is>
@@ -35642,17 +35672,17 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U596" t="inlineStr">
+      <c r="X596" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
       </c>
-      <c r="V596" t="inlineStr">
+      <c r="Y596" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
       </c>
-      <c r="W596" t="inlineStr">
+      <c r="Z596" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -35730,17 +35760,17 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U597" t="inlineStr">
+      <c r="X597" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
       </c>
-      <c r="V597" t="inlineStr">
+      <c r="Y597" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
       </c>
-      <c r="W597" t="inlineStr">
+      <c r="Z597" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -35818,17 +35848,17 @@
           <t>BLAISE Thibault</t>
         </is>
       </c>
-      <c r="U598" t="inlineStr">
+      <c r="X598" t="inlineStr">
         <is>
           <t>35388</t>
         </is>
       </c>
-      <c r="V598" t="inlineStr">
+      <c r="Y598" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="W598" t="inlineStr">
+      <c r="Z598" t="inlineStr">
         <is>
           <t>41589</t>
         </is>
@@ -35906,17 +35936,17 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U599" t="inlineStr">
+      <c r="X599" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
       </c>
-      <c r="V599" t="inlineStr">
+      <c r="Y599" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="W599" t="inlineStr">
+      <c r="Z599" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -35994,17 +36024,17 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U600" t="inlineStr">
+      <c r="X600" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
       </c>
-      <c r="V600" t="inlineStr">
+      <c r="Y600" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
       </c>
-      <c r="W600" t="inlineStr">
+      <c r="Z600" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -36072,17 +36102,17 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U601" t="inlineStr">
+      <c r="X601" t="inlineStr">
         <is>
           <t>35309</t>
         </is>
       </c>
-      <c r="V601" t="inlineStr">
+      <c r="Y601" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
       </c>
-      <c r="W601" t="inlineStr">
+      <c r="Z601" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -36160,7 +36190,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="V602" t="inlineStr">
+      <c r="Y602" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -36238,17 +36268,17 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U603" t="inlineStr">
+      <c r="X603" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
       </c>
-      <c r="V603" t="inlineStr">
+      <c r="Y603" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
       </c>
-      <c r="W603" t="inlineStr">
+      <c r="Z603" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -36326,17 +36356,17 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U604" t="inlineStr">
+      <c r="X604" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
       </c>
-      <c r="V604" t="inlineStr">
+      <c r="Y604" t="inlineStr">
         <is>
           <t>38435</t>
         </is>
       </c>
-      <c r="W604" t="inlineStr">
+      <c r="Z604" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -36414,17 +36444,17 @@
           <t>BREGAZZI Ella</t>
         </is>
       </c>
-      <c r="U605" t="inlineStr">
+      <c r="X605" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
       </c>
-      <c r="V605" t="inlineStr">
+      <c r="Y605" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
       </c>
-      <c r="W605" t="inlineStr">
+      <c r="Z605" t="inlineStr">
         <is>
           <t>41598</t>
         </is>
@@ -36502,12 +36532,12 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="V606" t="inlineStr">
+      <c r="Y606" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
       </c>
-      <c r="W606" t="inlineStr">
+      <c r="Z606" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -36585,17 +36615,17 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U607" t="inlineStr">
+      <c r="X607" t="inlineStr">
         <is>
           <t>37919</t>
         </is>
       </c>
-      <c r="V607" t="inlineStr">
+      <c r="Y607" t="inlineStr">
         <is>
           <t>43077</t>
         </is>
       </c>
-      <c r="W607" t="inlineStr">
+      <c r="Z607" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -36673,12 +36703,12 @@
           <t>MARTINS TAQUES Ricardo</t>
         </is>
       </c>
-      <c r="V608" t="inlineStr">
+      <c r="Y608" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
       </c>
-      <c r="W608" t="inlineStr">
+      <c r="Z608" t="inlineStr">
         <is>
           <t>38022</t>
         </is>
@@ -36756,12 +36786,12 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="V609" t="inlineStr">
+      <c r="Y609" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
       </c>
-      <c r="W609" t="inlineStr">
+      <c r="Z609" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -36839,12 +36869,12 @@
           <t>SHABANOV Maxim</t>
         </is>
       </c>
-      <c r="U610" t="inlineStr">
+      <c r="X610" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
       </c>
-      <c r="W610" t="inlineStr">
+      <c r="Z610" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
@@ -36912,17 +36942,17 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U611" t="inlineStr">
+      <c r="X611" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
       </c>
-      <c r="V611" t="inlineStr">
+      <c r="Y611" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
       </c>
-      <c r="W611" t="inlineStr">
+      <c r="Z611" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -36990,12 +37020,12 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="V612" t="inlineStr">
+      <c r="Y612" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
       </c>
-      <c r="W612" t="inlineStr">
+      <c r="Z612" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -37073,17 +37103,17 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U613" t="inlineStr">
+      <c r="X613" t="inlineStr">
         <is>
           <t>35346</t>
         </is>
       </c>
-      <c r="V613" t="inlineStr">
+      <c r="Y613" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="W613" t="inlineStr">
+      <c r="Z613" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -37161,17 +37191,17 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U614" t="inlineStr">
+      <c r="X614" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
       </c>
-      <c r="V614" t="inlineStr">
+      <c r="Y614" t="inlineStr">
         <is>
           <t>35295</t>
         </is>
       </c>
-      <c r="W614" t="inlineStr">
+      <c r="Z614" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -37249,17 +37279,17 @@
           <t>NABASKUES Unai</t>
         </is>
       </c>
-      <c r="U615" t="inlineStr">
+      <c r="X615" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
       </c>
-      <c r="V615" t="inlineStr">
+      <c r="Y615" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
       </c>
-      <c r="W615" t="inlineStr">
+      <c r="Z615" t="inlineStr">
         <is>
           <t>38775</t>
         </is>
@@ -37327,17 +37357,17 @@
           <t>SMITH Tyler</t>
         </is>
       </c>
-      <c r="U616" t="inlineStr">
+      <c r="X616" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
       </c>
-      <c r="V616" t="inlineStr">
+      <c r="Y616" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
       </c>
-      <c r="W616" t="inlineStr">
+      <c r="Z616" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
@@ -37415,12 +37445,12 @@
           <t>MERRITT Jaxon</t>
         </is>
       </c>
-      <c r="U617" t="inlineStr">
+      <c r="X617" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
       </c>
-      <c r="V617" t="inlineStr">
+      <c r="Y617" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -37498,17 +37528,17 @@
           <t>BEDA Marcello</t>
         </is>
       </c>
-      <c r="U618" t="inlineStr">
+      <c r="X618" t="inlineStr">
         <is>
           <t>35501</t>
         </is>
       </c>
-      <c r="V618" t="inlineStr">
+      <c r="Y618" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
       </c>
-      <c r="W618" t="inlineStr">
+      <c r="Z618" t="inlineStr">
         <is>
           <t>39899</t>
         </is>
@@ -37586,17 +37616,17 @@
           <t>SCIANIMANICO Tom</t>
         </is>
       </c>
-      <c r="U619" t="inlineStr">
+      <c r="X619" t="inlineStr">
         <is>
           <t>41590</t>
         </is>
       </c>
-      <c r="V619" t="inlineStr">
+      <c r="Y619" t="inlineStr">
         <is>
           <t>35584</t>
         </is>
       </c>
-      <c r="W619" t="inlineStr">
+      <c r="Z619" t="inlineStr">
         <is>
           <t>35675</t>
         </is>
@@ -37674,17 +37704,17 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U620" t="inlineStr">
+      <c r="X620" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
       </c>
-      <c r="V620" t="inlineStr">
+      <c r="Y620" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
       </c>
-      <c r="W620" t="inlineStr">
+      <c r="Z620" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -37762,17 +37792,17 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U621" t="inlineStr">
+      <c r="X621" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
       </c>
-      <c r="V621" t="inlineStr">
+      <c r="Y621" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
       </c>
-      <c r="W621" t="inlineStr">
+      <c r="Z621" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -37850,17 +37880,17 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U622" t="inlineStr">
+      <c r="X622" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
       </c>
-      <c r="V622" t="inlineStr">
+      <c r="Y622" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
       </c>
-      <c r="W622" t="inlineStr">
+      <c r="Z622" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -37938,17 +37968,17 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U623" t="inlineStr">
+      <c r="X623" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
       </c>
-      <c r="V623" t="inlineStr">
+      <c r="Y623" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
       </c>
-      <c r="W623" t="inlineStr">
+      <c r="Z623" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -38026,17 +38056,17 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U624" t="inlineStr">
+      <c r="X624" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
       </c>
-      <c r="V624" t="inlineStr">
+      <c r="Y624" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
       </c>
-      <c r="W624" t="inlineStr">
+      <c r="Z624" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -38296,7 +38326,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U629" t="inlineStr">
+      <c r="X629" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -38354,7 +38384,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U630" t="inlineStr">
+      <c r="X630" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -38412,7 +38442,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U631" t="inlineStr">
+      <c r="X631" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -38470,7 +38500,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U632" t="inlineStr">
+      <c r="X632" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -38528,7 +38558,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U633" t="inlineStr">
+      <c r="X633" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -38586,7 +38616,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U634" t="inlineStr">
+      <c r="X634" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -38644,7 +38674,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U635" t="inlineStr">
+      <c r="X635" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -38702,7 +38732,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U636" t="inlineStr">
+      <c r="X636" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -38760,7 +38790,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U637" t="inlineStr">
+      <c r="X637" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -38818,7 +38848,7 @@
           <t>MANGIN Estelle</t>
         </is>
       </c>
-      <c r="U638" t="inlineStr">
+      <c r="X638" t="inlineStr">
         <is>
           <t>35670</t>
         </is>
@@ -38876,7 +38906,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U639" t="inlineStr">
+      <c r="X639" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -38987,7 +39017,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U641" t="inlineStr">
+      <c r="X641" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -39045,7 +39075,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U642" t="inlineStr">
+      <c r="X642" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -39103,7 +39133,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U643" t="inlineStr">
+      <c r="X643" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -39161,7 +39191,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U644" t="inlineStr">
+      <c r="X644" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -39219,7 +39249,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U645" t="inlineStr">
+      <c r="X645" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -39277,7 +39307,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U646" t="inlineStr">
+      <c r="X646" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -39335,7 +39365,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U647" t="inlineStr">
+      <c r="X647" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -39393,7 +39423,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U648" t="inlineStr">
+      <c r="X648" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -39451,7 +39481,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U649" t="inlineStr">
+      <c r="X649" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -39509,7 +39539,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U650" t="inlineStr">
+      <c r="X650" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -39567,7 +39597,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U651" t="inlineStr">
+      <c r="X651" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -39625,7 +39655,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U652" t="inlineStr">
+      <c r="X652" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -39683,7 +39713,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U653" t="inlineStr">
+      <c r="X653" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -39741,7 +39771,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U654" t="inlineStr">
+      <c r="X654" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -39905,7 +39935,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U657" t="inlineStr">
+      <c r="X657" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -39963,7 +39993,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U658" t="inlineStr">
+      <c r="X658" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -40026,12 +40056,12 @@
           <t>SUSLOV Alexei</t>
         </is>
       </c>
-      <c r="U659" t="inlineStr">
+      <c r="X659" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
       </c>
-      <c r="V659" t="inlineStr">
+      <c r="Y659" t="inlineStr">
         <is>
           <t>35770</t>
         </is>
@@ -40094,12 +40124,12 @@
           <t>LARIONOV Dmitry</t>
         </is>
       </c>
-      <c r="U660" t="inlineStr">
+      <c r="X660" t="inlineStr">
         <is>
           <t>35449</t>
         </is>
       </c>
-      <c r="V660" t="inlineStr">
+      <c r="Y660" t="inlineStr">
         <is>
           <t>35450</t>
         </is>
@@ -40162,12 +40192,12 @@
           <t>KERVELLA Loic</t>
         </is>
       </c>
-      <c r="U661" t="inlineStr">
+      <c r="X661" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V661" t="inlineStr">
+      <c r="Y661" t="inlineStr">
         <is>
           <t>35672</t>
         </is>
@@ -40230,12 +40260,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U662" t="inlineStr">
+      <c r="X662" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V662" t="inlineStr">
+      <c r="Y662" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -40298,12 +40328,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U663" t="inlineStr">
+      <c r="X663" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V663" t="inlineStr">
+      <c r="Y663" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -40366,12 +40396,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U664" t="inlineStr">
+      <c r="X664" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V664" t="inlineStr">
+      <c r="Y664" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -40434,12 +40464,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U665" t="inlineStr">
+      <c r="X665" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V665" t="inlineStr">
+      <c r="Y665" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -40502,12 +40532,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U666" t="inlineStr">
+      <c r="X666" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V666" t="inlineStr">
+      <c r="Y666" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -40570,12 +40600,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U667" t="inlineStr">
+      <c r="X667" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V667" t="inlineStr">
+      <c r="Y667" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -40638,12 +40668,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U668" t="inlineStr">
+      <c r="X668" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V668" t="inlineStr">
+      <c r="Y668" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -40706,12 +40736,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U669" t="inlineStr">
+      <c r="X669" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V669" t="inlineStr">
+      <c r="Y669" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -40774,7 +40804,7 @@
           <t>HOUNSLOW Richard</t>
         </is>
       </c>
-      <c r="U670" t="inlineStr">
+      <c r="X670" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -40837,12 +40867,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U671" t="inlineStr">
+      <c r="X671" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V671" t="inlineStr">
+      <c r="Y671" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -40905,12 +40935,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U672" t="inlineStr">
+      <c r="X672" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V672" t="inlineStr">
+      <c r="Y672" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -40973,12 +41003,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U673" t="inlineStr">
+      <c r="X673" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V673" t="inlineStr">
+      <c r="Y673" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -41041,12 +41071,12 @@
           <t>SCIANIMANICO Nicolas</t>
         </is>
       </c>
-      <c r="U674" t="inlineStr">
+      <c r="X674" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
       </c>
-      <c r="V674" t="inlineStr">
+      <c r="Y674" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
@@ -41167,12 +41197,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U676" t="inlineStr">
+      <c r="X676" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V676" t="inlineStr">
+      <c r="Y676" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -41235,12 +41265,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U677" t="inlineStr">
+      <c r="X677" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V677" t="inlineStr">
+      <c r="Y677" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -41303,12 +41333,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U678" t="inlineStr">
+      <c r="X678" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V678" t="inlineStr">
+      <c r="Y678" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -41376,7 +41406,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U679" t="inlineStr">
+      <c r="X679" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -41444,7 +41474,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U680" t="inlineStr">
+      <c r="X680" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -41575,7 +41605,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U682" t="inlineStr">
+      <c r="X682" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -41643,7 +41673,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U683" t="inlineStr">
+      <c r="X683" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -41711,7 +41741,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U684" t="inlineStr">
+      <c r="X684" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -41842,7 +41872,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U686" t="inlineStr">
+      <c r="X686" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -41910,7 +41940,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U687" t="inlineStr">
+      <c r="X687" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -41978,7 +42008,7 @@
           <t>MANGIN Estelle</t>
         </is>
       </c>
-      <c r="U688" t="inlineStr">
+      <c r="X688" t="inlineStr">
         <is>
           <t>35670</t>
         </is>
@@ -42051,12 +42081,12 @@
           <t>SCIANIMANICO Nicolas</t>
         </is>
       </c>
-      <c r="U689" t="inlineStr">
+      <c r="X689" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
       </c>
-      <c r="V689" t="inlineStr">
+      <c r="Y689" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
@@ -42129,7 +42159,7 @@
           <t>HOUNSLOW Richard</t>
         </is>
       </c>
-      <c r="U690" t="inlineStr">
+      <c r="X690" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -42202,12 +42232,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U691" t="inlineStr">
+      <c r="X691" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V691" t="inlineStr">
+      <c r="Y691" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -42280,12 +42310,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U692" t="inlineStr">
+      <c r="X692" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V692" t="inlineStr">
+      <c r="Y692" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -42358,12 +42388,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U693" t="inlineStr">
+      <c r="X693" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V693" t="inlineStr">
+      <c r="Y693" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -42436,12 +42466,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U694" t="inlineStr">
+      <c r="X694" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V694" t="inlineStr">
+      <c r="Y694" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -42514,12 +42544,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U695" t="inlineStr">
+      <c r="X695" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V695" t="inlineStr">
+      <c r="Y695" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -42592,12 +42622,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U696" t="inlineStr">
+      <c r="X696" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V696" t="inlineStr">
+      <c r="Y696" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -42670,12 +42700,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U697" t="inlineStr">
+      <c r="X697" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V697" t="inlineStr">
+      <c r="Y697" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -42748,12 +42778,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U698" t="inlineStr">
+      <c r="X698" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V698" t="inlineStr">
+      <c r="Y698" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -42831,12 +42861,12 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U699" t="inlineStr">
+      <c r="X699" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
       </c>
-      <c r="W699" t="inlineStr">
+      <c r="Z699" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -42914,17 +42944,17 @@
           <t>DENHOLLANDER Jazmyne</t>
         </is>
       </c>
-      <c r="U700" t="inlineStr">
+      <c r="X700" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
       </c>
-      <c r="V700" t="inlineStr">
+      <c r="Y700" t="inlineStr">
         <is>
           <t>35533</t>
         </is>
       </c>
-      <c r="W700" t="inlineStr">
+      <c r="Z700" t="inlineStr">
         <is>
           <t>37165</t>
         </is>
@@ -43002,12 +43032,12 @@
           <t>CWIK Sara</t>
         </is>
       </c>
-      <c r="U701" t="inlineStr">
+      <c r="X701" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
       </c>
-      <c r="W701" t="inlineStr">
+      <c r="Z701" t="inlineStr">
         <is>
           <t>43978</t>
         </is>
@@ -43085,17 +43115,17 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U702" t="inlineStr">
+      <c r="X702" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
       </c>
-      <c r="V702" t="inlineStr">
+      <c r="Y702" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
       </c>
-      <c r="W702" t="inlineStr">
+      <c r="Z702" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -43173,17 +43203,17 @@
           <t>ZARUBOVA Kristina</t>
         </is>
       </c>
-      <c r="U703" t="inlineStr">
+      <c r="X703" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
       </c>
-      <c r="V703" t="inlineStr">
+      <c r="Y703" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
       </c>
-      <c r="W703" t="inlineStr">
+      <c r="Z703" t="inlineStr">
         <is>
           <t>39247</t>
         </is>
@@ -43261,7 +43291,7 @@
           <t>NEAVE Elizabeth</t>
         </is>
       </c>
-      <c r="U704" t="inlineStr">
+      <c r="X704" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -43339,17 +43369,17 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U705" t="inlineStr">
+      <c r="X705" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
       </c>
-      <c r="V705" t="inlineStr">
+      <c r="Y705" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
       </c>
-      <c r="W705" t="inlineStr">
+      <c r="Z705" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -43417,17 +43447,17 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U706" t="inlineStr">
+      <c r="X706" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
       </c>
-      <c r="V706" t="inlineStr">
+      <c r="Y706" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
       </c>
-      <c r="W706" t="inlineStr">
+      <c r="Z706" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -43495,17 +43525,17 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U707" t="inlineStr">
+      <c r="X707" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
       </c>
-      <c r="V707" t="inlineStr">
+      <c r="Y707" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
       </c>
-      <c r="W707" t="inlineStr">
+      <c r="Z707" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -43583,12 +43613,12 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="V708" t="inlineStr">
+      <c r="Y708" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
       </c>
-      <c r="W708" t="inlineStr">
+      <c r="Z708" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -43666,17 +43696,17 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U709" t="inlineStr">
+      <c r="X709" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
       </c>
-      <c r="V709" t="inlineStr">
+      <c r="Y709" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
       </c>
-      <c r="W709" t="inlineStr">
+      <c r="Z709" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -43754,17 +43784,17 @@
           <t>MANGIN Estelle</t>
         </is>
       </c>
-      <c r="U710" t="inlineStr">
+      <c r="X710" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
       </c>
-      <c r="V710" t="inlineStr">
+      <c r="Y710" t="inlineStr">
         <is>
           <t>35493</t>
         </is>
       </c>
-      <c r="W710" t="inlineStr">
+      <c r="Z710" t="inlineStr">
         <is>
           <t>35670</t>
         </is>
@@ -43829,17 +43859,62 @@
       </c>
       <c r="R711" t="inlineStr">
         <is>
-          <t>KARLOVSKY Ondrej/JANE Jakub</t>
+          <t>KARLOVSKY Ondrej</t>
         </is>
       </c>
       <c r="S711" t="inlineStr">
         <is>
-          <t>KASPAR Jonas/SINDLER Marek</t>
+          <t>JANE Jakub</t>
         </is>
       </c>
       <c r="T711" t="inlineStr">
         <is>
-          <t>KOPLIK Tomas/VRZAN Jakub</t>
+          <t>KASPAR Jonas</t>
+        </is>
+      </c>
+      <c r="U711" t="inlineStr">
+        <is>
+          <t>SINDLER Marek</t>
+        </is>
+      </c>
+      <c r="V711" t="inlineStr">
+        <is>
+          <t>KOPLIK Tomas</t>
+        </is>
+      </c>
+      <c r="W711" t="inlineStr">
+        <is>
+          <t>VRZAN Jakub</t>
+        </is>
+      </c>
+      <c r="X711" t="inlineStr">
+        <is>
+          <t>35060</t>
+        </is>
+      </c>
+      <c r="Y711" t="inlineStr">
+        <is>
+          <t>35061</t>
+        </is>
+      </c>
+      <c r="Z711" t="inlineStr">
+        <is>
+          <t>35062</t>
+        </is>
+      </c>
+      <c r="AA711" t="inlineStr">
+        <is>
+          <t>35063</t>
+        </is>
+      </c>
+      <c r="AB711" t="inlineStr">
+        <is>
+          <t>35042</t>
+        </is>
+      </c>
+      <c r="AC711" t="inlineStr">
+        <is>
+          <t>35043</t>
         </is>
       </c>
     </row>
@@ -43902,17 +43977,62 @@
       </c>
       <c r="R712" t="inlineStr">
         <is>
-          <t>SZCZEPANSKI Piotr/POCHWALA Marcin</t>
+          <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
       <c r="S712" t="inlineStr">
         <is>
-          <t>BRZEZINSKI Filip/BRZEZINSKI Andrzej</t>
+          <t>POCHWALA Marcin</t>
         </is>
       </c>
       <c r="T712" t="inlineStr">
         <is>
-          <t>WIERCIOCH Michal/MAJERCZAK Grzegorz</t>
+          <t>BRZEZINSKI Filip</t>
+        </is>
+      </c>
+      <c r="U712" t="inlineStr">
+        <is>
+          <t>BRZEZINSKI Andrzej</t>
+        </is>
+      </c>
+      <c r="V712" t="inlineStr">
+        <is>
+          <t>WIERCIOCH Michal</t>
+        </is>
+      </c>
+      <c r="W712" t="inlineStr">
+        <is>
+          <t>MAJERCZAK Grzegorz</t>
+        </is>
+      </c>
+      <c r="X712" t="inlineStr">
+        <is>
+          <t>35080</t>
+        </is>
+      </c>
+      <c r="Y712" t="inlineStr">
+        <is>
+          <t>35079</t>
+        </is>
+      </c>
+      <c r="Z712" t="inlineStr">
+        <is>
+          <t>35082</t>
+        </is>
+      </c>
+      <c r="AA712" t="inlineStr">
+        <is>
+          <t>35081</t>
+        </is>
+      </c>
+      <c r="AB712" t="inlineStr">
+        <is>
+          <t>35085</t>
+        </is>
+      </c>
+      <c r="AC712" t="inlineStr">
+        <is>
+          <t>35086</t>
         </is>
       </c>
     </row>
@@ -43965,17 +44085,42 @@
       </c>
       <c r="R713" t="inlineStr">
         <is>
-          <t>FLORENCE David/HOUNSLOW Richard</t>
+          <t>FLORENCE David</t>
         </is>
       </c>
       <c r="S713" t="inlineStr">
         <is>
-          <t>DAVIES Rhys/LISTER Matthew</t>
+          <t>HOUNSLOW Richard</t>
         </is>
       </c>
       <c r="T713" t="inlineStr">
         <is>
-          <t>BURGESS Adam/PITT Greg</t>
+          <t>DAVIES Rhys</t>
+        </is>
+      </c>
+      <c r="U713" t="inlineStr">
+        <is>
+          <t>LISTER Matthew</t>
+        </is>
+      </c>
+      <c r="V713" t="inlineStr">
+        <is>
+          <t>BURGESS Adam</t>
+        </is>
+      </c>
+      <c r="W713" t="inlineStr">
+        <is>
+          <t>PITT Greg</t>
+        </is>
+      </c>
+      <c r="X713" t="inlineStr">
+        <is>
+          <t>35634</t>
+        </is>
+      </c>
+      <c r="AB713" t="inlineStr">
+        <is>
+          <t>35647</t>
         </is>
       </c>
     </row>
@@ -44038,17 +44183,62 @@
       </c>
       <c r="R714" t="inlineStr">
         <is>
-          <t>HOCHSCHORNER Pavol/HOCHSCHORNER Peter</t>
+          <t>HOCHSCHORNER Pavol</t>
         </is>
       </c>
       <c r="S714" t="inlineStr">
         <is>
-          <t>SKANTAR Ladislav/SKANTAR Peter</t>
+          <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
       <c r="T714" t="inlineStr">
         <is>
-          <t>KUCERA Tomas/BATIK Jan</t>
+          <t>SKANTAR Ladislav</t>
+        </is>
+      </c>
+      <c r="U714" t="inlineStr">
+        <is>
+          <t>SKANTAR Peter</t>
+        </is>
+      </c>
+      <c r="V714" t="inlineStr">
+        <is>
+          <t>KUCERA Tomas</t>
+        </is>
+      </c>
+      <c r="W714" t="inlineStr">
+        <is>
+          <t>BATIK Jan</t>
+        </is>
+      </c>
+      <c r="X714" t="inlineStr">
+        <is>
+          <t>35356</t>
+        </is>
+      </c>
+      <c r="Y714" t="inlineStr">
+        <is>
+          <t>35357</t>
+        </is>
+      </c>
+      <c r="Z714" t="inlineStr">
+        <is>
+          <t>35360</t>
+        </is>
+      </c>
+      <c r="AA714" t="inlineStr">
+        <is>
+          <t>35361</t>
+        </is>
+      </c>
+      <c r="AB714" t="inlineStr">
+        <is>
+          <t>35368</t>
+        </is>
+      </c>
+      <c r="AC714" t="inlineStr">
+        <is>
+          <t>35367</t>
         </is>
       </c>
     </row>
@@ -44111,17 +44301,62 @@
       </c>
       <c r="R715" t="inlineStr">
         <is>
-          <t>CAILHOL Hugo/SCIANIMANICO Nicolas</t>
+          <t>CAILHOL Hugo</t>
         </is>
       </c>
       <c r="S715" t="inlineStr">
         <is>
-          <t>KLAUSS Gauthier/PECHE Matthieu</t>
+          <t>SCIANIMANICO Nicolas</t>
         </is>
       </c>
       <c r="T715" t="inlineStr">
         <is>
-          <t>PRIGENT Yves/KERVELLA Loic</t>
+          <t>KLAUSS Gauthier</t>
+        </is>
+      </c>
+      <c r="U715" t="inlineStr">
+        <is>
+          <t>PECHE Matthieu</t>
+        </is>
+      </c>
+      <c r="V715" t="inlineStr">
+        <is>
+          <t>PRIGENT Yves</t>
+        </is>
+      </c>
+      <c r="W715" t="inlineStr">
+        <is>
+          <t>KERVELLA Loic</t>
+        </is>
+      </c>
+      <c r="X715" t="inlineStr">
+        <is>
+          <t>35491</t>
+        </is>
+      </c>
+      <c r="Y715" t="inlineStr">
+        <is>
+          <t>35476</t>
+        </is>
+      </c>
+      <c r="Z715" t="inlineStr">
+        <is>
+          <t>35350</t>
+        </is>
+      </c>
+      <c r="AA715" t="inlineStr">
+        <is>
+          <t>35400</t>
+        </is>
+      </c>
+      <c r="AB715" t="inlineStr">
+        <is>
+          <t>35671</t>
+        </is>
+      </c>
+      <c r="AC715" t="inlineStr">
+        <is>
+          <t>35672</t>
         </is>
       </c>
     </row>
